--- a/artfynd/A 5233-2026 artfynd.xlsx
+++ b/artfynd/A 5233-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131422472</v>
       </c>
       <c r="B2" t="n">
-        <v>101224</v>
+        <v>101225</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>131422724</v>
       </c>
       <c r="B3" t="n">
-        <v>101224</v>
+        <v>101225</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>131422887</v>
       </c>
       <c r="B4" t="n">
-        <v>57181</v>
+        <v>57182</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>131422894</v>
       </c>
       <c r="B5" t="n">
-        <v>58014</v>
+        <v>58015</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>131422900</v>
       </c>
       <c r="B6" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>131422977</v>
       </c>
       <c r="B7" t="n">
-        <v>101224</v>
+        <v>101225</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 5233-2026 artfynd.xlsx
+++ b/artfynd/A 5233-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131422472</v>
       </c>
       <c r="B2" t="n">
-        <v>101225</v>
+        <v>101228</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>131422724</v>
       </c>
       <c r="B3" t="n">
-        <v>101225</v>
+        <v>101228</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>131422887</v>
       </c>
       <c r="B4" t="n">
-        <v>57182</v>
+        <v>57185</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>131422894</v>
       </c>
       <c r="B5" t="n">
-        <v>58015</v>
+        <v>58018</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>131422900</v>
       </c>
       <c r="B6" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>131422977</v>
       </c>
       <c r="B7" t="n">
-        <v>101225</v>
+        <v>101228</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 5233-2026 artfynd.xlsx
+++ b/artfynd/A 5233-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131422472</v>
       </c>
       <c r="B2" t="n">
-        <v>101228</v>
+        <v>101231</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>131422724</v>
       </c>
       <c r="B3" t="n">
-        <v>101228</v>
+        <v>101231</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>131422887</v>
       </c>
       <c r="B4" t="n">
-        <v>57185</v>
+        <v>57186</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>131422894</v>
       </c>
       <c r="B5" t="n">
-        <v>58018</v>
+        <v>58019</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>131422900</v>
       </c>
       <c r="B6" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>131422977</v>
       </c>
       <c r="B7" t="n">
-        <v>101228</v>
+        <v>101231</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 5233-2026 artfynd.xlsx
+++ b/artfynd/A 5233-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131422472</v>
+        <v>131422887</v>
       </c>
       <c r="B2" t="n">
-        <v>101257</v>
+        <v>57247</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>100038</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Brundins torp, Brundins torp, Srm</t>
+          <t>Hästhagen, Hästhagen, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>659525</v>
+        <v>659704</v>
       </c>
       <c r="R2" t="n">
-        <v>6545115</v>
+        <v>6545167</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131422724</v>
+        <v>131422900</v>
       </c>
       <c r="B3" t="n">
-        <v>101257</v>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,24 +798,29 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hästhagen, Hästhagen, Srm</t>
@@ -823,7 +833,7 @@
         <v>6545167</v>
       </c>
       <c r="S3" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -852,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131422887</v>
+        <v>131422894</v>
       </c>
       <c r="B4" t="n">
-        <v>57206</v>
+        <v>58082</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,16 +910,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100038</v>
+        <v>103035</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Kråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Corvus corone</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -920,7 +930,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -935,7 +945,7 @@
         <v>6545167</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -964,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,53 +1011,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131422894</v>
+        <v>131422472</v>
       </c>
       <c r="B5" t="n">
-        <v>58039</v>
+        <v>101325</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103035</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Corvus corone</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hästhagen, Hästhagen, Srm</t>
+          <t>Brundins torp, Brundins torp, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>659704</v>
+        <v>659525</v>
       </c>
       <c r="R5" t="n">
-        <v>6545167</v>
+        <v>6545115</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1076,7 +1081,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1086,7 +1091,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1113,40 +1118,35 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131422900</v>
+        <v>131422724</v>
       </c>
       <c r="B6" t="n">
-        <v>57909</v>
+        <v>101325</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hästhagen, Hästhagen, Srm</t>
@@ -1159,7 +1159,7 @@
         <v>6545167</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1228,7 +1228,7 @@
         <v>131422977</v>
       </c>
       <c r="B7" t="n">
-        <v>101257</v>
+        <v>101325</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 5233-2026 artfynd.xlsx
+++ b/artfynd/A 5233-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131422887</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131422900</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1008,6 +1023,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131422894</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1115,6 +1135,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131422472</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1222,6 +1247,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131422724</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1329,8 +1359,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131422977</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>